--- a/Dados/Brutos/pib_mesos.xlsx
+++ b/Dados/Brutos/pib_mesos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matheus-rosa\Documents\Projetos Python\proj_munic_sc\Dados\Brutos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matheus-rosa\Desktop\proj_munic_sc\Dados\Brutos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9966A9F-58DA-4247-896B-72836C457173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EDB9AA-8D70-4648-979B-517A1521A615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,7 +103,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -113,9 +113,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -422,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5395C4C9-D512-4238-8CC6-8F24136BF8C6}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -432,11 +429,9 @@
     <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" customWidth="1"/>
-    <col min="18" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
@@ -462,7 +457,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2002</v>
       </c>
@@ -476,7 +471,7 @@
         <v>17045455022.687239</v>
       </c>
       <c r="E2">
-        <v>74220392955.774338</v>
+        <v>74220392955.774323</v>
       </c>
       <c r="F2">
         <v>44641161658.702736</v>
@@ -488,9 +483,8 @@
         <f>SUM(B2:G2)</f>
         <v>302425135018.75562</v>
       </c>
-      <c r="K2" s="4"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2003</v>
       </c>
@@ -504,7 +498,7 @@
         <v>17497057995.955822</v>
       </c>
       <c r="E3">
-        <v>76230475406.964966</v>
+        <v>76230475406.964951</v>
       </c>
       <c r="F3">
         <v>44663933823.694687</v>
@@ -516,9 +510,8 @@
         <f t="shared" ref="H3:H23" si="0">SUM(B3:G3)</f>
         <v>310558754291.14539</v>
       </c>
-      <c r="K3" s="4"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2004</v>
       </c>
@@ -544,9 +537,8 @@
         <f t="shared" si="0"/>
         <v>331005528852.38477</v>
       </c>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>2005</v>
       </c>
@@ -572,9 +564,8 @@
         <f t="shared" si="0"/>
         <v>341992660193.98944</v>
       </c>
-      <c r="K5" s="4"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>2006</v>
       </c>
@@ -600,9 +591,8 @@
         <f t="shared" si="0"/>
         <v>348651317762.23779</v>
       </c>
-      <c r="K6" s="4"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>2007</v>
       </c>
@@ -628,9 +618,8 @@
         <f t="shared" si="0"/>
         <v>369958948013.79736</v>
       </c>
-      <c r="K7" s="4"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>2008</v>
       </c>
@@ -657,7 +646,7 @@
         <v>377545563445.64423</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>2009</v>
       </c>
@@ -671,7 +660,7 @@
         <v>18463594013.461834</v>
       </c>
       <c r="E9">
-        <v>101340732277.41859</v>
+        <v>101340732277.41861</v>
       </c>
       <c r="F9">
         <v>56515759134.105515</v>
@@ -681,10 +670,10 @@
       </c>
       <c r="H9">
         <f t="shared" si="0"/>
-        <v>374349220882.35931</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>374349220882.35938</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>2010</v>
       </c>
@@ -711,7 +700,7 @@
         <v>399481458028.1828</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>2011</v>
       </c>
@@ -738,7 +727,7 @@
         <v>414992864212.12299</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>2012</v>
       </c>
@@ -765,7 +754,7 @@
         <v>420574532562.07385</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>2013</v>
       </c>
@@ -776,7 +765,7 @@
         <v>97445821339.279785</v>
       </c>
       <c r="D13">
-        <v>20661731916.235603</v>
+        <v>20661731916.235607</v>
       </c>
       <c r="E13">
         <v>123902775352.02258</v>
@@ -785,14 +774,14 @@
         <v>66017841430.804932</v>
       </c>
       <c r="G13">
-        <v>48250967892.560783</v>
+        <v>48250967892.560768</v>
       </c>
       <c r="H13">
         <f t="shared" si="0"/>
         <v>435779698478.51636</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>2014</v>
       </c>
@@ -812,14 +801,14 @@
         <v>67940153513.893715</v>
       </c>
       <c r="G14">
-        <v>50147337056.987915</v>
+        <v>50147337056.987923</v>
       </c>
       <c r="H14">
         <f t="shared" si="0"/>
         <v>445572342639.14563</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>2015</v>
       </c>
@@ -830,7 +819,7 @@
         <v>95958865765.980316</v>
       </c>
       <c r="D15">
-        <v>21070925589.555279</v>
+        <v>21070925589.555275</v>
       </c>
       <c r="E15">
         <v>125642108213.89893</v>
@@ -846,7 +835,7 @@
         <v>430296409396.42755</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>2016</v>
       </c>
@@ -860,7 +849,7 @@
         <v>21389125780.430492</v>
       </c>
       <c r="E16">
-        <v>123136382101.83344</v>
+        <v>123136382101.8334</v>
       </c>
       <c r="F16">
         <v>65545741078.980606</v>
@@ -887,17 +876,17 @@
         <v>21757456136.340126</v>
       </c>
       <c r="E17">
-        <v>131512303464.36021</v>
+        <v>131512303464.36023</v>
       </c>
       <c r="F17">
         <v>66245294412.283478</v>
       </c>
       <c r="G17">
-        <v>49116360428.42086</v>
+        <v>49116360428.420868</v>
       </c>
       <c r="H17">
         <f t="shared" si="0"/>
-        <v>439122382722.46979</v>
+        <v>439122382722.46985</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -941,7 +930,7 @@
         <v>22255272573.450653</v>
       </c>
       <c r="E19">
-        <v>144071516499.64578</v>
+        <v>144071516499.64575</v>
       </c>
       <c r="F19">
         <v>71436460356.370193</v>
@@ -951,7 +940,7 @@
       </c>
       <c r="H19">
         <f t="shared" si="0"/>
-        <v>478130019279.25677</v>
+        <v>478130019279.25671</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -974,7 +963,7 @@
         <v>65374496885.211777</v>
       </c>
       <c r="G20">
-        <v>51502385410.351318</v>
+        <v>51502385410.351311</v>
       </c>
       <c r="H20">
         <f t="shared" si="0"/>
@@ -1001,7 +990,7 @@
         <v>67093153392.713005</v>
       </c>
       <c r="G21">
-        <v>53646517431.549454</v>
+        <v>53646517431.549461</v>
       </c>
       <c r="H21">
         <f t="shared" si="0"/>
@@ -1028,7 +1017,7 @@
         <v>69146784995.907547</v>
       </c>
       <c r="G22">
-        <v>54610616958.355545</v>
+        <v>54610616958.355553</v>
       </c>
       <c r="H22">
         <f t="shared" si="0"/>
@@ -1043,13 +1032,13 @@
         <v>90255351000</v>
       </c>
       <c r="C23">
-        <v>114991451000</v>
+        <v>116874219330.4287</v>
       </c>
       <c r="D23">
         <v>22980189000</v>
       </c>
       <c r="E23">
-        <v>155875673000</v>
+        <v>167787492964.7804</v>
       </c>
       <c r="F23">
         <v>72856424000</v>
@@ -1059,7 +1048,7 @@
       </c>
       <c r="H23">
         <f t="shared" si="0"/>
-        <v>513392972000</v>
+        <v>527187560295.20911</v>
       </c>
     </row>
   </sheetData>
